--- a/myprojects/ExelProj/AR_Aging_Report.xlsx
+++ b/myprojects/ExelProj/AR_Aging_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inanj\Documents\GitHub\inakm.github.io\myprojects\ExelProj\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C86211-1F57-4558-898B-649945DC0F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508C2A12-DBB6-411A-B337-6711E2EAE12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
   <si>
     <t>AUTOMATED ACCOUNTS RECEIVABLE AGING REPORT</t>
   </si>
@@ -217,6 +217,12 @@
   </si>
   <si>
     <t>Dell Tech</t>
+  </si>
+  <si>
+    <t>INV-012</t>
+  </si>
+  <si>
+    <t>HP Tech</t>
   </si>
 </sst>
 </file>
@@ -509,7 +515,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -631,10 +637,17 @@
     <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -683,19 +696,20 @@
     <xf numFmtId="165" fontId="15" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1128,114 +1142,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="43">
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="46">
         <f ca="1">TODAY()</f>
-        <v>46124</v>
-      </c>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
+        <v>46125</v>
+      </c>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
     </row>
     <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="46"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
     </row>
     <row r="4" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="48">
+      <c r="B4" s="51">
         <f>SUMIF(M8:M500,"&lt;&gt;Collected",L8:L500)</f>
-        <v>1064500</v>
-      </c>
-      <c r="C4" s="49" t="s">
+        <v>4386500</v>
+      </c>
+      <c r="C4" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="50">
+      <c r="D4" s="53">
         <f ca="1">SUMIF(K8:K500,"0-30 Days",L8:L500)</f>
-        <v>249000</v>
-      </c>
-      <c r="E4" s="51" t="s">
+        <v>3571000</v>
+      </c>
+      <c r="E4" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="52">
+      <c r="F4" s="55">
         <f ca="1">SUMIF(K8:K500,"31-60 Days",L8:L500)</f>
         <v>705500</v>
       </c>
-      <c r="G4" s="53" t="s">
+      <c r="G4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="54">
+      <c r="H4" s="57">
         <f ca="1">SUMIF(K8:K500,"61-90 Days",L8:L500)</f>
         <v>95000</v>
       </c>
-      <c r="I4" s="55" t="s">
+      <c r="I4" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="56">
+      <c r="J4" s="59">
         <f ca="1">SUMIF(K8:K500,"90+ Days",L8:L500)</f>
         <v>15000</v>
       </c>
-      <c r="K4" s="57" t="s">
+      <c r="K4" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="58">
+      <c r="L4" s="61">
         <f>SUMIF(M8:M500,"Collected",L8:L500)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="47"/>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
+      <c r="A5" s="50"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
     </row>
     <row r="6" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1346,17 +1360,17 @@
       </c>
       <c r="G9" s="13">
         <f ca="1">IF(D9="","",MAX(0,TODAY()-D9))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H9" s="14" t="str">
-        <f t="shared" ref="H9:H18" ca="1" si="1">IF(M9="Collected","Collected",IF(G9&lt;=30,"0-30 Days",IF(G9&lt;=60,"31-60 Days",IF(G9&lt;=90,"61-90 Days","90+ Days"))))</f>
+        <f t="shared" ref="H9:H19" ca="1" si="1">IF(M9="Collected","Collected",IF(G9&lt;=30,"0-30 Days",IF(G9&lt;=60,"31-60 Days",IF(G9&lt;=90,"61-90 Days","90+ Days"))))</f>
         <v>0-30 Days</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>23</v>
       </c>
       <c r="J9" s="8" t="str">
-        <f t="shared" ref="J9:J18" ca="1" si="2">IF(M9="Collected","Collected",IF(G9&gt;90,"HIGH RISK",IF(AND(G9&gt;60,I9="C"),"HIGH RISK",IF(G9&gt;60,"MEDIUM",IF(G9&gt;30,"LOW-MEDIUM","LOW")))))</f>
+        <f t="shared" ref="J9:J19" ca="1" si="2">IF(M9="Collected","Collected",IF(G9&gt;90,"HIGH RISK",IF(AND(G9&gt;60,I9="C"),"HIGH RISK",IF(G9&gt;60,"MEDIUM",IF(G9&gt;30,"LOW-MEDIUM","LOW")))))</f>
         <v>LOW</v>
       </c>
       <c r="K9" s="14" t="str">
@@ -1392,7 +1406,7 @@
       </c>
       <c r="G10" s="5">
         <f ca="1">IF(D10="","",MAX(0,TODAY()-D10))</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H10" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1437,8 +1451,8 @@
         <v>0</v>
       </c>
       <c r="G11" s="13">
-        <f t="shared" ref="G11:G18" ca="1" si="4">IF(D11="","",MAX(0,TODAY()-D11))</f>
-        <v>72</v>
+        <f t="shared" ref="G11:G19" ca="1" si="4">IF(D11="","",MAX(0,TODAY()-D11))</f>
+        <v>73</v>
       </c>
       <c r="H11" s="14" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1530,7 +1544,7 @@
       </c>
       <c r="G13" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H13" s="14" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1576,7 +1590,7 @@
       </c>
       <c r="G14" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H14" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1668,7 +1682,7 @@
       </c>
       <c r="G16" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H16" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1740,10 +1754,10 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="61" t="s">
+      <c r="A18" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="61" t="s">
+      <c r="B18" s="42" t="s">
         <v>58</v>
       </c>
       <c r="C18" s="11">
@@ -1752,21 +1766,21 @@
       <c r="D18" s="11">
         <v>46087</v>
       </c>
-      <c r="E18" s="62">
+      <c r="E18" s="43">
         <v>555000</v>
       </c>
-      <c r="F18" s="62">
+      <c r="F18" s="43">
         <v>55000</v>
       </c>
       <c r="G18" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H18" s="14" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>31-60 Days</v>
       </c>
-      <c r="I18" s="63" t="s">
+      <c r="I18" s="44" t="s">
         <v>36</v>
       </c>
       <c r="J18" s="8" t="str">
@@ -1778,18 +1792,64 @@
         <v>31-60 Days</v>
       </c>
       <c r="L18" s="16">
-        <f t="shared" si="3"/>
+        <f>IF(M18="Collected",0,E18-F18)</f>
         <v>500000</v>
       </c>
-      <c r="M18" s="63" t="s">
+      <c r="M18" s="44" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E20" s="60"/>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="64" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="11">
+        <v>46072</v>
+      </c>
+      <c r="D19" s="11">
+        <v>46111</v>
+      </c>
+      <c r="E19" s="65">
+        <v>3400000</v>
+      </c>
+      <c r="F19" s="65">
+        <v>78000</v>
+      </c>
+      <c r="G19" s="13">
+        <f ca="1">IF(D19="","",MAX(0,TODAY()-D19))</f>
+        <v>14</v>
+      </c>
+      <c r="H19" s="14" t="str">
+        <f ca="1">IF(M19="Collected","Collected",IF(G19&lt;=30,"0-30 Days",IF(G19&lt;=60,"31-60 Days",IF(G19&lt;=90,"61-90 Days","90+ Days"))))</f>
+        <v>0-30 Days</v>
+      </c>
+      <c r="I19" s="67" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" s="8" t="str">
+        <f ca="1">IF(M19="Collected","Collected",IF(G19&gt;90,"HIGH RISK",IF(AND(G19&gt;60,I19="C"),"HIGH RISK",IF(G19&gt;60,"MEDIUM",IF(G19&gt;30,"LOW-MEDIUM","LOW")))))</f>
+        <v>LOW</v>
+      </c>
+      <c r="K19" s="14" t="str">
+        <f ca="1">H19</f>
+        <v>0-30 Days</v>
+      </c>
+      <c r="L19" s="16">
+        <f>IF(M19="Collected",0,E19-F19)</f>
+        <v>3322000</v>
+      </c>
+      <c r="M19" s="67" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E24" s="66"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E25" s="59"/>
+      <c r="E25" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1865,7 +1925,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.88671875" bestFit="1" customWidth="1"/>
@@ -1875,26 +1935,26 @@
     <col min="5" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="str">
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="63" t="str">
         <f ca="1">"As of: "&amp;TEXT('AR Aging Tracker'!E2,"DD-MMM-YYYY")</f>
-        <v>As of: 12-Apr-2026</v>
-      </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-    </row>
-    <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>As of: 13-Apr-2026</v>
+      </c>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+    </row>
+    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>15</v>
       </c>
@@ -1911,27 +1971,27 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="19">
         <f ca="1">COUNTIF('AR Aging Tracker'!H8:H500,"0-30 Days")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="20">
         <f ca="1">SUMIF('AR Aging Tracker'!H8:H500,"0-30 Days",'AR Aging Tracker'!L8:L500)</f>
-        <v>249000</v>
+        <v>3571000</v>
       </c>
       <c r="D5" s="21">
         <f ca="1">IFERROR(C5/C10,0)</f>
-        <v>0.23391263503992485</v>
+        <v>0.81408868118089595</v>
       </c>
       <c r="E5" s="18" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>4</v>
       </c>
@@ -1945,13 +2005,13 @@
       </c>
       <c r="D6" s="25">
         <f ca="1">IFERROR(C6/C10,0)</f>
-        <v>0.66275246594645376</v>
+        <v>0.16083437820585889</v>
       </c>
       <c r="E6" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
         <v>5</v>
       </c>
@@ -1965,13 +2025,13 @@
       </c>
       <c r="D7" s="29">
         <f ca="1">IFERROR(C7/C10,0)</f>
-        <v>8.9243776420854862E-2</v>
+        <v>2.1657357802348114E-2</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="30" t="s">
         <v>52</v>
       </c>
@@ -1985,13 +2045,13 @@
       </c>
       <c r="D8" s="33">
         <f ca="1">IFERROR(C8/C10,0)</f>
-        <v>1.4091122592766557E-2</v>
+        <v>3.4195828108970704E-3</v>
       </c>
       <c r="E8" s="30" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
         <v>7</v>
       </c>
@@ -2011,19 +2071,19 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="38" t="s">
         <v>55</v>
       </c>
       <c r="B10" s="39">
         <f>COUNTA('AR Aging Tracker'!A8:A500)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="40">
         <f>SUMIF('AR Aging Tracker'!M8:M500,"&lt;&gt;Collected",'AR Aging Tracker'!L8:L500)</f>
-        <v>1064500</v>
-      </c>
-      <c r="D10" s="65">
+        <v>4386500</v>
+      </c>
+      <c r="D10" s="45">
         <f ca="1">SUM(D5:D9)</f>
         <v>1</v>
       </c>
@@ -2031,94 +2091,13 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="64"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-    </row>
-    <row r="12" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="64"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-    </row>
-    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="64"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-    </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="64"/>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-    </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="64"/>
-      <c r="B15" s="64"/>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-    </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="64"/>
-      <c r="B16" s="64"/>
-      <c r="C16" s="64"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64"/>
-      <c r="F16" s="64"/>
-    </row>
-    <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="64"/>
-      <c r="B17" s="64"/>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="64"/>
-    </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="64"/>
-      <c r="B18" s="64"/>
-      <c r="C18" s="64"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64"/>
-      <c r="F18" s="64"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="64"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="64"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="64"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="64"/>
-      <c r="B20" s="64"/>
-      <c r="C20" s="64"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="64"/>
-      <c r="B21" s="64"/>
-      <c r="C21" s="64"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-    </row>
+    <row r="12" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
